--- a/OMOP Analysis/Results/Output_yearly_costs_OMOP-Boot.xlsx
+++ b/OMOP Analysis/Results/Output_yearly_costs_OMOP-Boot.xlsx
@@ -504,13 +504,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>635.04</v>
+        <v>523.458</v>
       </c>
       <c r="C2">
-        <v>624.912</v>
+        <v>514.785</v>
       </c>
       <c r="D2">
-        <v>645.035</v>
+        <v>532.2089999999999</v>
       </c>
     </row>
     <row r="3">
@@ -518,13 +518,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>361.967</v>
+        <v>299.039</v>
       </c>
       <c r="C3">
-        <v>353.6</v>
+        <v>291.733</v>
       </c>
       <c r="D3">
-        <v>370.686</v>
+        <v>306.595</v>
       </c>
     </row>
   </sheetData>
@@ -564,13 +564,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>654.008</v>
+        <v>676.162</v>
       </c>
       <c r="C2">
-        <v>643.792</v>
+        <v>665.443</v>
       </c>
       <c r="D2">
-        <v>663.75</v>
+        <v>687.044</v>
       </c>
     </row>
     <row r="3">
@@ -578,13 +578,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>372.778</v>
+        <v>386.298</v>
       </c>
       <c r="C3">
-        <v>364.325</v>
+        <v>377.433</v>
       </c>
       <c r="D3">
-        <v>381.797</v>
+        <v>395.171</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/Output_yearly_costs_OMOP-Boot.xlsx
+++ b/OMOP Analysis/Results/Output_yearly_costs_OMOP-Boot.xlsx
@@ -384,13 +384,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>537.877</v>
+        <v>597.575</v>
       </c>
       <c r="C2">
-        <v>529.765</v>
+        <v>590.207</v>
       </c>
       <c r="D2">
-        <v>546.09</v>
+        <v>605.006</v>
       </c>
     </row>
     <row r="3">
@@ -398,13 +398,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>291.88</v>
+        <v>316.057</v>
       </c>
       <c r="C3">
-        <v>284.957</v>
+        <v>309.442</v>
       </c>
       <c r="D3">
-        <v>298.727</v>
+        <v>322.371</v>
       </c>
     </row>
   </sheetData>
@@ -444,13 +444,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>560.909</v>
+        <v>614.232</v>
       </c>
       <c r="C2">
-        <v>552.9400000000001</v>
+        <v>606.7</v>
       </c>
       <c r="D2">
-        <v>568.998</v>
+        <v>621.726</v>
       </c>
     </row>
     <row r="3">
@@ -458,13 +458,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>304.378</v>
+        <v>324.867</v>
       </c>
       <c r="C3">
-        <v>297.043</v>
+        <v>318.729</v>
       </c>
       <c r="D3">
-        <v>311.474</v>
+        <v>331.195</v>
       </c>
     </row>
   </sheetData>
@@ -504,13 +504,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>523.458</v>
+        <v>577.574</v>
       </c>
       <c r="C2">
-        <v>514.785</v>
+        <v>569.1130000000001</v>
       </c>
       <c r="D2">
-        <v>532.2089999999999</v>
+        <v>585.78</v>
       </c>
     </row>
     <row r="3">
@@ -518,13 +518,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>299.039</v>
+        <v>321.139</v>
       </c>
       <c r="C3">
-        <v>291.733</v>
+        <v>314.365</v>
       </c>
       <c r="D3">
-        <v>306.595</v>
+        <v>327.885</v>
       </c>
     </row>
   </sheetData>
@@ -564,13 +564,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>676.162</v>
+        <v>749.201</v>
       </c>
       <c r="C2">
-        <v>665.443</v>
+        <v>739.379</v>
       </c>
       <c r="D2">
-        <v>687.044</v>
+        <v>758.961</v>
       </c>
     </row>
     <row r="3">
@@ -578,13 +578,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>386.298</v>
+        <v>416.864</v>
       </c>
       <c r="C3">
-        <v>377.433</v>
+        <v>408.433</v>
       </c>
       <c r="D3">
-        <v>395.171</v>
+        <v>425.252</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/Output_yearly_costs_OMOP-Boot.xlsx
+++ b/OMOP Analysis/Results/Output_yearly_costs_OMOP-Boot.xlsx
@@ -384,13 +384,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>597.575</v>
+        <v>2565.907</v>
       </c>
       <c r="C2">
-        <v>590.207</v>
+        <v>2531.565</v>
       </c>
       <c r="D2">
-        <v>605.006</v>
+        <v>2600.374</v>
       </c>
     </row>
     <row r="3">
@@ -398,13 +398,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>316.057</v>
+        <v>1378.489</v>
       </c>
       <c r="C3">
-        <v>309.442</v>
+        <v>1347.558</v>
       </c>
       <c r="D3">
-        <v>322.371</v>
+        <v>1408.383</v>
       </c>
     </row>
   </sheetData>
@@ -444,13 +444,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>614.232</v>
+        <v>2312.518</v>
       </c>
       <c r="C2">
-        <v>606.7</v>
+        <v>2280.653</v>
       </c>
       <c r="D2">
-        <v>621.726</v>
+        <v>2343.017</v>
       </c>
     </row>
     <row r="3">
@@ -458,13 +458,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>324.867</v>
+        <v>1285.955</v>
       </c>
       <c r="C3">
-        <v>318.729</v>
+        <v>1259.424</v>
       </c>
       <c r="D3">
-        <v>331.195</v>
+        <v>1312.226</v>
       </c>
     </row>
   </sheetData>
@@ -504,13 +504,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>577.574</v>
+        <v>3082.903</v>
       </c>
       <c r="C2">
-        <v>569.1130000000001</v>
+        <v>3040.647</v>
       </c>
       <c r="D2">
-        <v>585.78</v>
+        <v>3123.74</v>
       </c>
     </row>
     <row r="3">
@@ -518,13 +518,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>321.139</v>
+        <v>1737.546</v>
       </c>
       <c r="C3">
-        <v>314.365</v>
+        <v>1701.587</v>
       </c>
       <c r="D3">
-        <v>327.885</v>
+        <v>1774.478</v>
       </c>
     </row>
   </sheetData>
@@ -564,13 +564,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>749.201</v>
+        <v>2702.42</v>
       </c>
       <c r="C2">
-        <v>739.379</v>
+        <v>2662.751</v>
       </c>
       <c r="D2">
-        <v>758.961</v>
+        <v>2742.885</v>
       </c>
     </row>
     <row r="3">
@@ -578,13 +578,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>416.864</v>
+        <v>1549.01</v>
       </c>
       <c r="C3">
-        <v>408.433</v>
+        <v>1514.075</v>
       </c>
       <c r="D3">
-        <v>425.252</v>
+        <v>1583.584</v>
       </c>
     </row>
   </sheetData>
